--- a/医疗机器人产业地图/医疗机器人企业投资地图20260820.xlsx
+++ b/医疗机器人产业地图/医疗机器人企业投资地图20260820.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>18 家（顶尖国家级手术机器人研发制造实体与高校转化平台）</t>
+          <t>19 家（顶尖国家级手术机器人研发制造实体与高校转化平台）</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>每家收录企业均穿透匹配其核心技术源头高校（清华、交大、北航、哈工大、天大、苏大、港中文、华西医院等）及国家重点实验室/两院院士领军团队。</t>
+          <t>每家收录企业均穿透匹配其核心技术源头高校（清华、交大、北航、哈工大、天大、重大、苏大、港中文、华西医院等）及国家重点实验室/两院院士领军团队。</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -718,42 +718,42 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>成都博恩思医学机器人有限公司</t>
+          <t>诺孚泰智能科技（成都）有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>四川本土对标达芬奇的微创腹腔镜手术机器人</t>
+          <t>四川本土对标并超越达芬奇四臂系统的五臂双操控腔镜机器人</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统</t>
+          <t>免气腹实时力反馈五臂双操控微创腔镜手术机器人</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
+          <t>独创串并混联构型机械臂设计、双操控台同步主刀协作、免气腹物理悬吊微创技术、刚性传动降本</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
+          <t>重庆大学机械与运载工程学院 / 成都天府国际生物城研发制造基地（5000㎡）</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
+          <t>柏龙 教授（重庆大学博导/诺孚泰创始人兼董事长）</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
+          <t>完成中日友好医院实验动物肝胆联合切除术验证，全面推进NMPA创新医疗器械申报与人体临床试验</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
+          <t>完成Pre-A+轮数千万元融资（创投基金重点投资）</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -768,8 +768,8 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>https://www.biomems.com.cn
-http://www.wchscu.cn</t>
+          <t>https://www.cqu.edu.cn
+https://www.bio-tianfu.com</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -784,61 +784,127 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
+          <t>成都博恩思医学机器人有限公司</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>四川本土对标达芬奇的微创腹腔镜手术机器人</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.biomems.com.cn
+http://www.wchscu.cn</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>四川华西精创医疗科技有限公司</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>四川本地顶尖医工转化标杆（对标美敦力StealthStation）</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>“华西精准”骨科手术导航系统 / 经皮穿刺与胸外科微创手术定位机器人</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>光学三维空间立体定位、脊柱/关节穿刺轨迹智能规划、医用机械臂微创导向</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>四川大学华西医院 / 国家精准医学产业创新中心</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>裴福兴 教授（华西骨科领军）、李为民 教授（华西呼吸内科领军）</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>依托华西医院多中心临床资源推进三类医疗器械注册与规模化临床试验</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>华西医院科技成果转化实体（省属产业基金战略孵化）</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>四川省</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>http://www.wchscu.cn
 https://www.scu.edu.cn</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -902,7 +968,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>北京术锐技术、北京天智航医疗、华科精准（北京）医疗有限公司、北京柏惠维康、唯迈医疗（北京/天津）有限公司、真健康（北京）医疗有限公司</t>
+          <t>北京术锐技术、北京天智航、华科精准（北京）有限公司、北京柏惠维康科技、唯迈（北京/天津）有限公司、真健康（北京）有限公司</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1128,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>上海微创医疗机器人（集团）、直观复星医疗器械技术（上海）有限公司、上海奥朋医疗有限公司</t>
+          <t>上海微创医疗机器人、直观复星医疗器械技术（上海）有限公司、上海奥朋有限公司</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1148,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>苏州键嘉医疗、苏州迪凯尔医疗有限公司</t>
+          <t>苏州键嘉、苏州迪凯尔有限公司</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1328,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>深圳市精锋医疗、康诺思腾（Cornerstone Robotics）、元化智能（深圳）有限公司</t>
+          <t>深圳市精锋、康诺思腾（Cornerstone Robotics）、元化（深圳）有限公司</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1399,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1342,7 +1408,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>成都博恩思医学机器人有限公司、四川华西精创医疗有限公司</t>
+          <t>诺孚泰（成都）有限公司、成都博恩思医学机器人有限公司、四川华西精创有限公司</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2130,42 +2196,42 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>成都博恩思医学机器人有限公司</t>
+          <t>诺孚泰智能科技（成都）有限公司</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>四川本土对标达芬奇的微创腹腔镜手术机器人</t>
+          <t>四川本土对标并超越达芬奇四臂系统的五臂双操控腔镜机器人</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统</t>
+          <t>免气腹实时力反馈五臂双操控微创腔镜手术机器人</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
+          <t>独创串并混联构型机械臂设计、双操控台同步主刀协作、免气腹物理悬吊微创技术、刚性传动降本</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
+          <t>重庆大学机械与运载工程学院 / 成都天府国际生物城研发制造基地（5000㎡）</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
+          <t>柏龙 教授（重庆大学博导/诺孚泰创始人兼董事长）</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
+          <t>完成中日友好医院实验动物肝胆联合切除术验证，全面推进NMPA创新医疗器械申报与人体临床试验</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
+          <t>完成Pre-A+轮数千万元融资（创投基金重点投资）</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -2180,8 +2246,8 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>https://www.biomems.com.cn
-http://www.wchscu.cn</t>
+          <t>https://www.cqu.edu.cn
+https://www.bio-tianfu.com</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -2196,58 +2262,58 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>北京天智航医疗科技股份有限公司</t>
+          <t>成都博恩思医学机器人有限公司</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>对标史赛克Mako / 骨科领域“达芬奇级”多关节主从操作机器人</t>
+          <t>四川本土对标达芬奇的微创腹腔镜手术机器人</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>“天玑”（TiRobot 1.0/2.0/3.0）骨科手术机器人系统</t>
+          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>六自由度医用高精机械臂、光学空间定位双目双模跟踪、术中三维规划导航</t>
+          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>北京航空航天大学机器人研究所 / 北京积水潭医院</t>
+          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>田伟 院士（中国工程院院士/原积水潭医院院长）、张送根 博士、刘达 教授</t>
+          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>取得多张NMPA三类医疗器械注册证，入选国家重点研发计划，全国装机量第一（超6万例）</t>
+          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>科创板上市公司（688277）</t>
+          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tinavi.com
-https://www.buaa.edu.cn</t>
+          <t>https://www.biomems.com.cn
+http://www.wchscu.cn</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -2262,58 +2328,58 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>苏州键嘉医疗科技股份有限公司</t>
+          <t>北京天智航医疗科技股份有限公司</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>对标史赛克Mako / 硬组织高精度切削手术机器人</t>
+          <t>对标史赛克Mako / 骨科领域“达芬奇级”多关节主从操作机器人</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>“ARTHROBOT”髋膝一体全关节置换手术机器人 / “THETA”种植牙机器人</t>
+          <t>“天玑”（TiRobot 1.0/2.0/3.0）骨科手术机器人系统</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>主动力控骨质切削机械臂、双目亚毫米级红外空间跟踪、智能截骨规划算法</t>
+          <t>六自由度医用高精机械臂、光学空间定位双目双模跟踪、术中三维规划导航</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>苏州大学医疗机器人研究所 / 俄罗斯工程院协同基地</t>
+          <t>北京航空航天大学机器人研究所 / 北京积水潭医院</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>孙立宁 院士（俄罗斯工程院外籍院士/苏大机电学院院长）、宋生林 博士</t>
+          <t>田伟 院士（中国工程院院士/原积水潭医院院长）、张送根 博士、刘达 教授</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>ARTHROBOT髋膝关节机器人均取得NMPA创新三类注册证，实现髋膝一体化商业装机</t>
+          <t>取得多张NMPA三类医疗器械注册证，入选国家重点研发计划，全国装机量第一（超6万例）</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>拟IPO（高瓴/软银/百度/国药资本联合投资）</t>
+          <t>科创板上市公司（688277）</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>江苏省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>https://www.join-jia.com
-https://www.suda.edu.cn</t>
+          <t>https://www.tinavi.com
+https://www.buaa.edu.cn</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -2328,58 +2394,58 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>元化智能科技（深圳）有限公司</t>
+          <t>苏州键嘉医疗科技股份有限公司</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>骨科硬组织多专科“全自主切削与磨削”手术机器人</t>
+          <t>对标史赛克Mako / 硬组织高精度切削手术机器人</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>“锟铻”（KUNWU）全骨科手术机器人系统（髋/膝/单髁/脊柱全覆盖）</t>
+          <t>“ARTHROBOT”髋膝一体全关节置换手术机器人 / “THETA”种植牙机器人</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>全自主研发六自由度协作机械臂、双目光学导航定位仪、高动态骨组织边界保护算法</t>
+          <t>主动力控骨质切削机械臂、双目亚毫米级红外空间跟踪、智能截骨规划算法</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>南方科技大学机器人研究院 / 香港中文大学</t>
+          <t>苏州大学医疗机器人研究所 / 俄罗斯工程院协同基地</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>孟广耀 教授（创始人兼首席科学家）、孟庆虎 院士</t>
+          <t>孙立宁 院士（俄罗斯工程院外籍院士/苏大机电学院院长）、宋生林 博士</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>全膝置换、全髋置换及单髁置换均获NMPA三类注册证，实现骨科多亚专科全覆盖</t>
+          <t>ARTHROBOT髋膝关节机器人均取得NMPA创新三类注册证，实现髋膝一体化商业装机</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>拟IPO（红杉中国/深创投联合领投）</t>
+          <t>拟IPO（高瓴/软银/百度/国药资本联合投资）</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>江苏省</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>https://www.genextech.cn
-https://www.sustech.edu.cn</t>
+          <t>https://www.join-jia.com
+https://www.suda.edu.cn</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -2394,58 +2460,58 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>华科精准（北京）医疗科技有限公司</t>
+          <t>元化智能科技（深圳）有限公司</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>脑部微创外科“达芬奇级”高精度脑立体定向穿刺与消融系统</t>
+          <t>骨科硬组织多专科“全自主切削与磨削”手术机器人</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>华科精准“SR / Q300”神经外科手术机器人 / 磁共振引导LITT激光消融系统</t>
+          <t>“锟铻”（KUNWU）全骨科手术机器人系统（髋/膝/单髁/脊柱全覆盖）</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>颅脑多模态影像三维融合、亚毫米级立体定向机械臂定位、术中激光微创热消融闭环</t>
+          <t>全自主研发六自由度协作机械臂、双目光学导航定位仪、高动态骨组织边界保护算法</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>清华大学医学院 / 首都医科大学宣武医院 / 北京天坛医院</t>
+          <t>南方科技大学机器人研究院 / 香港中文大学</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>赵国光 教授（宣武医院院长）、张建民 教授（天坛医院脑科领军）</t>
+          <t>孟广耀 教授（创始人兼首席科学家）、孟庆虎 院士</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部三甲脑科中心</t>
+          <t>全膝置换、全髋置换及单髁置换均获NMPA三类注册证，实现骨科多亚专科全覆盖</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>完成数亿元D轮（美敦力/红杉中国/高瓴联合投资）</t>
+          <t>拟IPO（红杉中国/深创投联合领投）</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>https://www.sinovation.com
-https://www.tsinghua.edu.cn</t>
+          <t>https://www.genextech.cn
+https://www.sustech.edu.cn</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -2460,42 +2526,42 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>北京柏惠维康科技股份有限公司</t>
+          <t>华科精准（北京）医疗科技有限公司</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>中国最早脑立体定向手术机器人研发团队（对标法国ROSA）</t>
+          <t>脑部微创外科“达芬奇级”高精度脑立体定向穿刺与消融系统</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>“睿米”（Remebot）神经外科手术机器人 / “瑞医博”口腔种植手术机器人</t>
+          <t>华科精准“SR / Q300”神经外科手术机器人 / 磁共振引导LITT激光消融系统</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>无框架脑立体定向机械臂规划、微创多自由度导向定位、口腔亚毫米自主种植</t>
+          <t>颅脑多模态影像三维融合、亚毫米级立体定向机械臂定位、术中激光微创热消融闭环</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>北京航空航天大学机器人研究所 / 海军总医院</t>
+          <t>清华大学医学院 / 首都医科大学宣武医院 / 北京天坛医院</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>王田苗 教授（北航机器人所名誉所长）、刘达 教授、刘文博 团队</t>
+          <t>赵国光 教授（宣武医院院长）、张建民 教授（天坛医院脑科领军）</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>获得国内首张神经外科三类医疗器械注册证，多款产品实现NMPA三类认证与全国装机</t>
+          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部脑科中心</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>完成D轮融资（大钲资本/中信建投/天士力资本）</t>
+          <t>完成数亿元D轮（美敦力/红杉中国/高瓴联合投资）</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -2510,8 +2576,8 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>https://www.remebot.com
-https://www.buaa.edu.cn</t>
+          <t>https://www.sinovation.com
+https://www.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -2526,42 +2592,42 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>唯迈医疗科技（北京/天津）有限公司</t>
+          <t>北京柏惠维康科技股份有限公司</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>直接对标西门子Corindus血管介入手术机器人</t>
+          <t>中国最早脑立体定向手术机器人研发团队（对标法国ROSA）</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>“ETcath”血管介入手术机器人系统 / 极光平板DSA大型微创造影平台</t>
+          <t>“睿米”（Remebot）神经外科手术机器人 / “瑞医博”口腔种植手术机器人</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>介入导管导丝多自由度智能推进操控、微小力觉触觉双向反馈、全流程低剂量防辐射操控</t>
+          <t>无框架脑立体定向机械臂规划、微创多自由度导向定位、口腔亚毫米自主种植</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>北京理工大学医工融合研究院 / 日本工程院院士工作站</t>
+          <t>北京航空航天大学机器人研究所 / 海军总医院</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>郭书祥 院士（日本工程院院士/北理工教授）、杨海宏 博士</t>
+          <t>王田苗 教授（北航机器人所名誉所长）、刘达 教授、刘文博 团队</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类注册证并完成多中心PCI人体手术</t>
+          <t>获得国内首张神经外科三类医疗器械注册证，多款产品实现NMPA三类认证与全国装机</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>完成数亿元D轮融资（国药资本/华兴资本/浩悦资本）</t>
+          <t>完成D轮融资（大钲资本/中信建投/天士力资本）</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -2576,8 +2642,8 @@
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>https://www.wemedmed.com
-https://www.bit.edu.cn</t>
+          <t>https://www.remebot.com
+https://www.buaa.edu.cn</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -2592,58 +2658,58 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>上海奥朋医疗科技有限公司</t>
+          <t>唯迈医疗科技（北京/天津）有限公司</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>对标西门子Corindus / 泛血管主从遥操作介入手术机器人</t>
+          <t>直接对标西门子Corindus血管介入手术机器人</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>“ALLVAS”泛血管介入手术机器人系统（冠脉/外周/脑血管全覆盖）</t>
+          <t>“ETcath”血管介入手术机器人系统 / 极光平板DSA大型微创造影平台</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>多轴主从力反馈介入执行端、多规格导丝导管通用夹持机构、亚毫米级送丝步进控制</t>
+          <t>介入导管导丝多自由度智能推进操控、微小力觉触觉双向反馈、全流程低剂量防辐射操控</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>复旦大学附属中山医院心内科 / 上海交通大学</t>
+          <t>北京理工大学医工融合研究院 / 日本工程院院士工作站</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>葛均波 院士（中国科学院院士/中山医院心内科主任）、刘冰 博士</t>
+          <t>郭书祥 院士（日本工程院院士/北理工教授）、杨海宏 博士</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>进入NMPA创新医疗器械特别审批程序，成功完成多例人体冠脉微创PCI手术</t>
+          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类注册证并完成多中心PCI人体手术</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>完成超亿元B轮融资（高瓴创投/保诺资本投资）</t>
+          <t>完成数亿元D轮融资（国药资本/华兴资本/浩悦资本）</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>https://www.allwamed.com
-http://www.zs-hospital.sh.cn</t>
+          <t>https://www.wemedmed.com
+https://www.bit.edu.cn</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -2658,58 +2724,58 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>真健康（北京）医疗科技有限公司</t>
+          <t>上海奥朋医疗科技有限公司</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>经皮穿刺与肿瘤微创介入“达芬奇级”多自由度机械臂消融系统</t>
+          <t>对标西门子Corindus / 泛血管主从遥操作介入手术机器人</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>“穿刺手术导航定位系统” / 经皮穿刺活检消融手术机器人</t>
+          <t>“ALLVAS”泛血管介入手术机器人系统（冠脉/外周/脑血管全覆盖）</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>CT/超声术中多模态影像三维融合、呼吸运动补偿追踪、高柔顺性穿刺机械臂控制</t>
+          <t>多轴主从力反馈介入执行端、多规格导丝导管通用夹持机构、亚毫米级送丝步进控制</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>清华大学 / 中国医学科学院肿瘤医院</t>
+          <t>复旦大学附属中山医院心内科 / 上海交通大学</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>张世阳 博士（联合创始人兼CTO）、国内肿瘤微创介入专家团队</t>
+          <t>葛均波 院士（中国科学院院士/中山医院心内科主任）、刘冰 博士</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>获NMPA创新医疗器械三类注册证，在全国头部三甲医院开展数千例肺结节精准活检手术</t>
+          <t>进入NMPA创新医疗器械特别审批程序，成功完成多例人体冠脉微创PCI手术</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>完成数亿元B+轮与Pre-IPO融资</t>
+          <t>完成超亿元B轮融资（高瓴创投/保诺资本投资）</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>https://www.truemed-tech.com
-https://www.tsinghua.edu.cn</t>
+          <t>https://www.allwamed.com
+http://www.zs-hospital.sh.cn</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2724,58 +2790,58 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>四川华西精创医疗科技有限公司</t>
+          <t>真健康（北京）医疗科技有限公司</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>四川本地顶尖医工转化标杆（对标美敦力StealthStation）</t>
+          <t>经皮穿刺与肿瘤微创介入“达芬奇级”多自由度机械臂消融系统</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>“华西精准”骨科手术导航系统 / 经皮穿刺与胸外科微创手术定位机器人</t>
+          <t>“穿刺手术导航定位系统” / 经皮穿刺活检消融手术机器人</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>光学三维空间立体定位、脊柱/关节穿刺轨迹智能规划、医用机械臂微创导向</t>
+          <t>CT/超声术中多模态影像三维融合、呼吸运动补偿追踪、高柔顺性穿刺机械臂控制</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>四川大学华西医院 / 国家精准医学产业创新中心</t>
+          <t>清华大学 / 中国医学科学院肿瘤医院</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>裴福兴 教授（华西骨科领军）、李为民 教授（华西呼吸内科领军）</t>
+          <t>张世阳 博士（联合创始人兼CTO）、国内肿瘤微创介入专家团队</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>依托华西医院多中心临床资源推进三类医疗器械注册与规模化临床试验</t>
+          <t>获NMPA创新医疗器械三类注册证，在全国头部三甲医院开展数千例肺结节精准活检手术</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>华西医院科技成果转化实体（省属产业基金战略孵化）</t>
+          <t>完成数亿元B+轮与Pre-IPO融资</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>http://www.wchscu.cn
-https://www.scu.edu.cn</t>
+          <t>https://www.truemed-tech.com
+https://www.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -2790,61 +2856,127 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
+          <t>四川华西精创医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>四川本地顶尖医工转化标杆（对标美敦力StealthStation）</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>“华西精准”骨科手术导航系统 / 经皮穿刺与胸外科微创手术定位机器人</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>光学三维空间立体定位、脊柱/关节穿刺轨迹智能规划、医用机械臂微创导向</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>四川大学华西医院 / 国家精准医学产业创新中心</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>裴福兴 教授（华西骨科领军）、李为民 教授（华西呼吸内科领军）</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>依托华西医院多中心临床资源推进三类医疗器械注册与规模化临床试验</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>华西医院科技成果转化实体（省属产业基金战略孵化）</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>http://www.wchscu.cn
+https://www.scu.edu.cn</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>苏州迪凯尔医疗科技有限公司</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>硬组织高精度口腔专科“达芬奇级”自主种植手术机器人</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>“易植美”（DCarer）口腔种植手术机器人 / 光学三维手术导航系统</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>光学高频双目空间追踪、全自主种植切削轨迹伺服、口腔微空间力觉安全边界保护</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>苏州大学机电工程学院 / 空军军医大学第三附属医院（口腔医学院）</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>陈新湖 博士（创始人兼CEO）、赵铱民 院士团队产学研协同</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>获NMPA三类医疗器械注册证，在全国数百家口腔专科医院规模化临床装机</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>拟IPO（完成数亿元C轮融资）</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>江苏省</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>苏州</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>https://www.dcarer.com
 https://www.suda.edu.cn</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3114,7 +3246,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部三甲脑科中心</t>
+          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部脑科中心</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">

--- a/医疗机器人产业地图/医疗机器人企业投资地图20260820.xlsx
+++ b/医疗机器人产业地图/医疗机器人企业投资地图20260820.xlsx
@@ -14,9 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑龙江省" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上海市" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="江苏省" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="山东省" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="广东省" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四川省" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="浙江省" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="山东省" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="广东省" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四川省" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,7 +553,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>19 家（顶尖国家级手术机器人研发制造实体与高校转化平台）</t>
+          <t>28 家（全国对标达芬奇及国际顶级手术机器人的核心实体企业与高校研发转化中心）</t>
         </is>
       </c>
     </row>
@@ -564,19 +565,19 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>【不在多，而在精确】。严格聚焦对标直观外科达芬奇（Da Vinci Xi/SP）及史赛克Mako等全球顶级手术机器人的中国自主研发实体、旗舰产品与源头高校重点实验室/临床转化中心。</t>
+          <t>【不在多，而在精确】。严格聚焦对标直观外科达芬奇（Da Vinci Xi/SP）、史赛克Mako、美敦力Mazor/Stealth、西门子Corindus等全球顶尖外科手术机器人的中国自主研发实体、旗舰产品与源头高校重点实验室/临床转化中心。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>技术赛道准入</t>
+          <t>五大核心赛道</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1. 软组织腔镜微创多臂主从遥操作手术机器人（对标达芬奇Xi/Si）；2. 单孔蛇形连续体微创手术机器人（对标达芬奇SP）；3. 骨科多自由度高精关节/脊柱切削手术机器人（对标史赛克Mako）；4. 神经外科脑立体定向与磁共振引导LITT激光消融系统（对标法国ROSA/美敦力）；5. 血管与心脏介入手术机器人（对标西门子Corindus）；6. 高精度经皮穿刺与专科硬组织自主种植机器人。</t>
+          <t>1. 软组织腔镜微创多臂主从遥操作手术机器人（对标达芬奇Xi/Si）；2. 单孔蛇形连续体微创手术机器人（对标达芬奇SP）；3. 骨科与脊柱多自由度高精切削与主动置针手术机器人（对标史赛克Mako/美敦力Mazor）；4. 神经外科脑立体定向与磁共振引导LITT激光消融系统（对标法国ROSA/美敦力Visualase）；5. 血管与心脏介入手术机器人（对标西门子Corindus）；6. 经皮穿刺与肿瘤微创消融手术机器人。</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>每家收录企业均穿透匹配其核心技术源头高校（清华、交大、北航、哈工大、天大、重大、苏大、港中文、华西医院等）及国家重点实验室/两院院士领军团队。</t>
+          <t>每家收录企业均穿透匹配其核心技术源头高校（清华、上海交大、北航、哈工大、天大、重大、浙大、苏大、港中文、南科大、华西医院等）及国家重点实验室/两院院士领军团队。</t>
         </is>
       </c>
     </row>
@@ -612,7 +613,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>国家药品监督管理局（NMPA）三类医疗器械注册库、CMDE创新医疗器械审批公示、国家重点研发计划智能机器人专项、各高校官方主页及上市公司公告。</t>
+          <t>国家药品监督管理局（NMPA）三类医疗器械注册库、CMDE创新医疗器械特别审查审批公示、国家重点研发计划智能机器人专项、各高校官方主页及上市公司公告。</t>
         </is>
       </c>
     </row>
@@ -627,22 +628,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -658,55 +660,60 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -718,61 +725,66 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>诺孚泰智能科技（成都）有限公司</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>四川本土对标并超越达芬奇四臂系统的五臂双操控腔镜机器人</t>
+          <t>深圳市精锋医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>免气腹实时力反馈五臂双操控微创腔镜手术机器人</t>
+          <t>直接对标达芬奇Xi（多孔）与达芬奇SP（单孔）双产品线</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>独创串并混联构型机械臂设计、双操控台同步主刀协作、免气腹物理悬吊微创技术、刚性传动降本</t>
+          <t>精锋“MP1000”多孔腔镜手术机器人 / “SP1000”单孔腔镜手术机器人</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>重庆大学机械与运载工程学院 / 成都天府国际生物城研发制造基地（5000㎡）</t>
+          <t>主从双向遥操作系统、高分辨率3D电子内窥镜、全自主自研伺服多自由度手术臂</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>柏龙 教授（重庆大学博导/诺孚泰创始人兼董事长）</t>
+          <t>香港中文大学天石机器人研究所 / 南方科技大学</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>完成中日友好医院实验动物肝胆联合切除术验证，全面推进NMPA创新医疗器械申报与人体临床试验</t>
+          <t>王建辰 博士（创始人兼董事长）、孟庆虎 院士、刘云辉 教授</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>完成Pre-A+轮数千万元融资（创投基金重点投资）</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>四川省</t>
+          <t>MP1000多孔及SP1000单孔均获NMPA三类医疗器械注册证，实现多孔/单孔双证闭环</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>港股上市推进中（淡马锡/红杉中国/腾讯/博裕联合投资）</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cqu.edu.cn
-https://www.bio-tianfu.com</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.edge-medical.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -784,61 +796,66 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>成都博恩思医学机器人有限公司</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>四川本土对标达芬奇的微创腹腔镜手术机器人</t>
+          <t>康诺思腾（Cornerstone Robotics）</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统</t>
+          <t>直接对标达芬奇高端多专科微创手术系统</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
+          <t>“Sentire”多孔及单孔微创腔镜手术机器人系统</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
+          <t>自主柔性连续体动力传动、模块化轻量化机械臂、全自主底层软硬件平台</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
+          <t>香港中文大学机械与自动化工程学系 / 深圳研发制造基地</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
+          <t>欧国威 教授（前达芬奇原厂Intuitive核心研发总监/港中文教授）</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>四川省</t>
+          <t>获得NMPA三类医疗器械注册证与CE认证，全球多中心临床手术开展</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>拟IPO（获美敦力/高瓴/启明/创新工场数亿元投资）</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>https://www.biomems.com.cn
-http://www.wchscu.cn</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cornerstonerobotics.com
+https://www.cuhk.edu.hk</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -850,61 +867,523 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>四川华西精创医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>四川本地顶尖医工转化标杆（对标美敦力StealthStation）</t>
+          <t>唯精医疗机器人（广东/浙江）有限公司</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>“华西精准”骨科手术导航系统 / 经皮穿刺与胸外科微创手术定位机器人</t>
+          <t>直接对标达芬奇Xi（微创器械+耗材生态深度协同）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>光学三维空间立体定位、脊柱/关节穿刺轨迹智能规划、医用机械臂微创导向</t>
+          <t>“康基唯精”腹腔镜微创手术机器人系统（SR01-200）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>四川大学华西医院 / 国家精准医学产业创新中心</t>
+          <t>多孔/单孔腹腔镜主从遥操作、微创多自由度吻合钳与分离剪、主手力觉传感</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>裴福兴 教授（华西骨科领军）、李为民 教授（华西呼吸内科领军）</t>
+          <t>浙江大学生物医学工程与仪器科学学院 / 广州开发区智造基地</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>依托华西医院多中心临床资源推进三类医疗器械注册与规模化临床试验</t>
+          <t>微精医疗联合创始人团队、浙江大学医工交叉科学家团队</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>华西医院科技成果转化实体（省属产业基金战略孵化）</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
+          <t>SR01-200获得NMPA三类医疗器械注册证，在全国多家医院开展高难度普外泌尿微创手术</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>完成亿元级B+轮融资（微创外科龙头康基医疗战略投资）</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.weijing-robot.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>元化智能科技（深圳）有限公司</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>骨科硬组织多专科“全自主切削与磨削”手术机器人（对标Mako）</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>“锟铻”（KUNWU）全骨科手术机器人系统（髋/膝/单髁/脊柱全覆盖）</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>全自主研发六自由度协作机械臂、双目光学导航定位仪、高动态骨组织边界保护算法</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>南方科技大学机器人研究院 / 香港中文大学</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>孟广耀 教授（创始人兼首席科学家）、孟庆虎 院士</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>全膝置换、全髋置换及单髁置换均获NMPA三类注册证，实现骨科多亚专科全覆盖</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>拟IPO（红杉中国/深创投联合领投）</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>https://www.genextech.cn
+https://www.sustech.edu.cn</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>深圳市鑫君特智能医疗器械有限公司</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>中国首款具备“导航+主动置针操作”全智能骨科手术机器人（对标Mazor）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>“ORTHBOT®”智能脊柱骨科手术机器人系统</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>多模态影像融合、自动钉道规划、主动进针伺服控制、压力监测防破壁保护</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>中国科学院深圳先进技术研究院 / 深圳市脊柱微创工程中心</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>姜轶 董事长兼研发带头人、国内顶级脊柱骨科专家团队</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>获得NMPA三类医疗器械注册证，并于2023年斩获中国首张欧盟MDR CE认证脊柱机器人证书</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元B轮与战略融资（知名医疗创投基金投资）</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.futurtec.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>企业名称</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>对标国际标杆（达芬奇等）</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>旗舰手术机器人产品</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>核心技术路线与优势</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>依托高校院所研发平台</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>科学家/学术带头人</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>临床注册/NMPA阶段</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>资本与融资背景</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>所属省份</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>总部城市</t>
+        </is>
+      </c>
+      <c r="M1" s="10" t="inlineStr">
+        <is>
+          <t>公开来源</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>核验日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>诺孚泰智能科技（成都）有限公司</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>四川本土对标并超越达芬奇四臂系统的五臂双操控腔镜机器人</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>免气腹实时力反馈五臂双操控微创腔镜手术机器人</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>独创串并混联构型机械臂设计、双操控台同步主刀协作、免气腹物理悬吊微创技术、刚性传动降本</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>重庆大学机械与运载工程学院 / 成都天府国际生物城研发制造基地（5000㎡）</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>柏龙 教授（重庆大学博导/诺孚泰创始人兼董事长）</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>完成中日友好医院实验动物肝胆联合切除术验证，全面推进NMPA创新医疗器械申报与人体临床试验</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>完成Pre-A+轮数千万元融资（成都市与天府生物城创投重点支持）</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>四川省</t>
         </is>
       </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cqu.edu.cn
+https://www.bio-tianfu.com</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>成都博恩思医学机器人有限公司</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>四川本土对标达芬奇的多孔微创腹腔镜及经自然腔道手术系统</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统（TORSS）</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.biomems.com.cn
+http://www.wchscu.cn</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>四川华西精创医疗科技有限公司 / 华西医疗机器人研究院</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>四川本地登顶《Science Robotics》顶刊的柔性脊柱与骨科导航微创手术机器人</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>“MicroSpine”柔性脊柱微创手术机器人 / 华西精准骨科手术导航系统</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>超冗余柔性连续体机械臂、微创经皮穿刺自动轨迹规划、多模态光学三维空间立体定位</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>四川大学华西医院 / 华西医疗机器人研究院 / 国家精准医学产业创新中心</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>裴福兴 教授（华西骨科领军/中华骨科分会前主委）、李为民 教授</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>MicroSpine成果发表于《Science Robotics》，骨科导航与穿刺系统推进三类器械注册申报</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>成都高新区岷山行动计划资助（华西医院科技成果转化实体）</t>
+        </is>
+      </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>http://www.wchscu.cn
 https://www.scu.edu.cn</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -959,7 +1438,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -968,7 +1447,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>北京术锐技术、北京天智航、华科精准（北京）有限公司、北京柏惠维康科技、唯迈（北京/天津）有限公司、真健康（北京）有限公司</t>
+          <t>北京术锐技术、北京天智航、北京长木谷、北京和华瑞博有限公司、北京罗森博特科技有限公司、华科精准（北京）有限公司、北京柏惠维康科技、北京华志微创、唯迈（北京/天津）有限公司、真健康（北京）有限公司</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1598,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -1128,7 +1607,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>上海微创医疗机器人、直观复星医疗器械技术（上海）有限公司、上海奥朋有限公司</t>
+          <t>直观复星医疗器械技术（上海）有限公司、上海微创医疗机器人、瑞龙诺赋（上海）有限公司（Ronovo Surgical）、上海奥朋有限公司</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1618,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -1148,7 +1627,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>苏州键嘉、苏州迪凯尔有限公司</t>
+          <t>苏州键嘉、苏州铸正机器人有限公司、苏州梅奥心磁有限公司</t>
         </is>
       </c>
     </row>
@@ -1158,17 +1637,17 @@
           <t>浙江省</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>0</v>
+      <c r="B12" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>暂无达芬奇级重点收录</t>
+          <t>已收录</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>持续追踪国际与国家重大专项</t>
+          <t>杭州佳量有限公司</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1798,7 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1328,7 +1807,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>深圳市精锋、康诺思腾（Cornerstone Robotics）、元化（深圳）有限公司</t>
+          <t>深圳市精锋、康诺思腾（Cornerstone Robotics）、唯精医疗机器人（广东/浙江）有限公司、元化（深圳）有限公司、深圳市鑫君特智能医疗器械有限公司</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1887,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>诺孚泰（成都）有限公司、成都博恩思医学机器人有限公司、四川华西精创有限公司</t>
+          <t>诺孚泰（成都）有限公司、成都博恩思医学机器人有限公司、四川华西精创有限公司 / 华西医疗机器人研究院</t>
         </is>
       </c>
     </row>
@@ -1643,22 +2122,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1674,55 +2154,60 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -1734,61 +2219,66 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上海微创医疗机器人（集团）股份有限公司</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇（Da Vinci Xi/Si）多孔腔镜手术系统</t>
+          <t>直观复星医疗器械技术（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>“图迈”（Toumai）多孔腔镜手术机器人 / “鸿鹄”骨科手术机器人</t>
+          <t>全球手术机器人绝对黄金标杆（达芬奇原厂中国本土化制造基地）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>多臂微创腹腔镜主从遥操作系统、高精度主手控制台、裸眼3D立体内窥镜</t>
+          <t>达芬奇“Da Vinci Xi / SP”国产化手术系统制造与创新研发</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>上海交通大学医疗机器人研究院 / 中科院微系统所</t>
+          <t>四臂主从遥操作系统、EndoWrist多自由度仿真手腕、高清沉浸式3D双目内窥镜</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>何超 博士（上海微创机器人总裁）、戴尅戎 院士团队</t>
+          <t>直观复星张江创新研发制造基地 / 复旦大学附属中山医院医工转化中心</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>图迈多孔获NMPA三类注册证（中国首个覆盖泌尿、普外、胸外、妇科全科室腔镜机器人）；鸿鹄获NMPA+FDA+CE认证</t>
+          <t>Intuitive全球科学家团队 + 葛均波/樊嘉 院士团队</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>港股上市公司（02252.HK）</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
+          <t>达芬奇Xi系统获NMPA国产化三类医疗器械注册证，在上海张江正式实现国产化量产下线</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>达芬奇原厂Intuitive Surgical与复星医药合资</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>上海市</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.medrobotics.com
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.intuitive-fosun.com
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1800,61 +2290,66 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>北京术锐技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇SP（Da Vinci Single Port）单孔手术系统</t>
+          <t>上海微创医疗机器人（集团）股份有限公司</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>“术锐”（Surgerii SR-CNS-100）单孔腔镜手术机器人</t>
+          <t>直接对标达芬奇（Da Vinci Xi/Si）多孔腔镜微创手术系统</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>高刚性蛇形连续体结构机构、多自由度微创蛇形器械、单孔多通道主从操控</t>
+          <t>“图迈”（Toumai）多孔腔镜手术机器人 / “鸿鹄”骨科手术机器人</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>上海交通大学机械与动力工程学院机器人研究所</t>
+          <t>多臂微创腹腔镜主从遥操作系统、高精度主手控制台、裸眼3D立体内窥镜</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>徐凯 教授（交大博导/术锐创始人兼首席科学家）</t>
+          <t>上海交通大学医疗机器人研究院 / 中科院微系统所</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>国内首个获批NMPA三类注册证的蛇形臂单孔腔镜手术系统（进入国家创新医疗器械特别审查绿色通道）</t>
+          <t>何超 博士（上海微创机器人总裁）、戴尅戎 院士团队</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>拟IPO（完成C轮数亿元融资，美敦力/国投招商投资）</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>北京市</t>
+          <t>图迈多孔获NMPA三类注册证（中国首个覆盖泌尿、普外、胸外、妇科全科室腔镜机器人）；鸿鹄获NMPA+FDA+CE认证</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>港股上市公司（02252.HK）</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>https://www.surgerii.com
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.medrobotics.com
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1866,61 +2361,66 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>深圳市精锋医疗科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇Xi（多孔）与达芬奇SP（单孔）双产品线</t>
+          <t>北京术锐技术股份有限公司</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>精锋“MP1000”多孔腔镜手术机器人 / “SP1000”单孔腔镜手术机器人</t>
+          <t>直接对标达芬奇SP（Da Vinci Single Port）单孔手术系统</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>主从双向遥操作系统、高分辨率3D电子内窥镜、全自主自研伺服多自由度手术臂</t>
+          <t>“术锐”（Surgerii SR-CNS-100/SR-ENS-600）单孔腔镜手术机器人</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>香港中文大学天石机器人研究所 / 南方科技大学</t>
+          <t>高刚性蛇形连续体结构机构、多自由度微创蛇形器械、单孔多通道主从操控</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>王建辰 博士（创始人兼董事长）、孟庆虎 院士、刘云辉 教授</t>
+          <t>上海交通大学机械与动力工程学院机器人研究所</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>MP1000多孔及SP1000单孔均获NMPA三类医疗器械注册证，实现多孔/单孔双证闭环</t>
+          <t>徐凯 教授（交大博导/国家杰青/术锐创始人兼首席科学家）</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>拟IPO（淡马锡/红杉中国/腾讯/博裕联合投资）</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>广东省</t>
+          <t>国内首个获批NMPA三类注册证的蛇形臂单孔腔镜手术系统（进入国家创新医疗器械特别审查绿色通道）</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>拟IPO（完成C轮数亿元融资，美敦力/国投招商投资）</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.edge-medical.com
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.surgerii.com
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1932,61 +2432,66 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>哈尔滨思哲睿智能医疗设备股份有限公司</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇（Da Vinci Xi）多孔腹腔镜手术系统</t>
+          <t>深圳市精锋医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>“康多机器人”（KangDuo Robot KD-SR-01/02）多孔及单孔腹腔镜手术系统</t>
+          <t>直接对标达芬奇Xi（多孔）与达芬奇SP（单孔）双产品线</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>主从构型空间解耦控制、开放式医生控制台、自适应从动多臂协作机构</t>
+          <t>精锋“MP1000”多孔腔镜手术机器人 / “SP1000”单孔腔镜手术机器人</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>哈尔滨工业大学机器人技术与系统国家重点实验室</t>
+          <t>主从双向遥操作系统、高分辨率3D电子内窥镜、全自主自研伺服多自由度手术臂</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>杜志江 教授（哈工大机器人所副所长/思哲睿首席科学家）、孙立宁 院士</t>
+          <t>香港中文大学天石机器人研究所 / 南方科技大学</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>获国家创新医疗器械特别审查，取得多张NMPA三类医疗器械注册证，累计完成数千例手术</t>
+          <t>王建辰 博士（创始人兼董事长）、孟庆虎 院士、刘云辉 教授</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>科创板申报（深创投/中金资本投资）</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>黑龙江省</t>
+          <t>MP1000多孔及SP1000单孔均获NMPA三类医疗器械注册证，实现多孔/单孔双证闭环</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>港股上市推进中（淡马锡/红杉中国/腾讯/博裕联合投资）</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>哈尔滨</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>https://www.hit.edu.cn
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>https://www.edge-medical.com
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1998,61 +2503,66 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>山东威高手术机器人有限公司</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>中国首个自主研发主从腔镜手术系统（对标达芬奇Xi）</t>
+          <t>哈尔滨思哲睿智能医疗设备股份有限公司</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>“妙手S”（MicroHand S）多孔微创腹腔镜手术机器人系统</t>
+          <t>直接对标达芬奇（Da Vinci Xi）多孔腹腔镜手术系统</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>多自由度微创手术末端器械、主从异构映射算法、5G超远程手术通信操控</t>
+          <t>“康多机器人”（KangDuo Robot KD-SR-01/02）多孔及单孔腹腔镜手术系统</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>天津大学机械工程学院 / 重庆大学</t>
+          <t>主从构型空间解耦控制、开放式医生控制台、自适应从动多臂协作机构</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>王树新 院士（中国工程院院士/原天大副校长/重大校长）</t>
+          <t>哈尔滨工业大学机器人技术与系统国家重点实验室</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>国内首批获批NMPA三类注册证的国产腹腔镜手术机器人，完成国际首例5G远程人体手术</t>
+          <t>杜志江 教授（哈工大机器人所副所长/思哲睿首席科学家）、孙立宁 院士</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>威高骨干产业实体（威高集团核心高端板块）</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>山东省</t>
+          <t>获国家创新医疗器械特别审查，取得多张NMPA三类医疗器械注册证与首张CB证书，完成数千例手术</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>科创板申报（深创投/中金资本投资）</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>威海</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.wego.com.cn
-https://www.tju.edu.cn</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
+          <t>黑龙江省</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hit.edu.cn
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2064,61 +2574,66 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>康诺思腾（Cornerstone Robotics）</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇高端多专科微创手术系统</t>
+          <t>山东威高手术机器人有限公司</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>“Sentire”多孔及单孔微创腔镜手术机器人系统</t>
+          <t>中国首个自主研发主从腔镜手术系统（对标达芬奇Xi）</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>自主柔性连续体动力传动、模块化轻量化机械臂、全自主底层软硬件平台</t>
+          <t>“妙手S”（MicroHand S）多孔微创腹腔镜手术机器人系统</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>香港中文大学机械与自动化工程学系 / 深圳研发基地</t>
+          <t>多自由度微创手术末端器械、主从异构映射算法、5G超远程手术通信操控</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>欧国威 教授（前达芬奇原厂Intuitive核心研发总监/港中文教授）</t>
+          <t>天津大学机械工程学院 / 重庆大学</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>获得NMPA三类医疗器械注册证与CE认证，全球多中心临床手术开展</t>
+          <t>王树新 院士（中国工程院院士/原天大副校长/重大校长）</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>拟IPO（获美敦力/高瓴/启明/创新工场数亿元投资）</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>广东省</t>
+          <t>国内首批获批NMPA三类注册证的国产腹腔镜手术机器人，完成国际首例5G远程人体手术</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>威高骨干产业实体（威高集团核心高端板块）</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>https://www.cornerstonerobotics.com
-https://www.cuhk.edu.hk</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>威海</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.wego.com.cn
+https://www.tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2130,61 +2645,66 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>直观复星医疗器械技术（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>全球手术机器人绝对黄金标杆（达芬奇原厂中国本土化制造）</t>
+          <t>康诺思腾（Cornerstone Robotics）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>达芬奇“Da Vinci Xi / SP”国产化手术系统制造与创新研发</t>
+          <t>直接对标达芬奇高端多专科微创手术系统</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>四臂主从遥操作系统、EndoWrist多自由度仿真手腕、高清沉浸式3D双目内窥镜</t>
+          <t>“Sentire”多孔及单孔微创腔镜手术机器人系统</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>直观复星张江创新研发基地 / 复旦大学附属中山医院医工转化中心</t>
+          <t>自主柔性连续体动力传动、模块化轻量化机械臂、全自主底层软硬件平台</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>全球Intuitive工程研发科学家团队 + 葛均波/樊嘉 院士团队</t>
+          <t>香港中文大学机械与自动化工程学系 / 深圳研发制造基地</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>达芬奇Xi系统获NMPA国产化三类医疗器械注册证，在上海张江正式实现国产化量产下线</t>
+          <t>欧国威 教授（前达芬奇原厂Intuitive核心研发总监/港中文教授）</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>达芬奇原厂Intuitive Surgical与复星医药合资</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>上海市</t>
+          <t>获得NMPA三类医疗器械注册证与CE认证，全球多中心临床手术开展</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>拟IPO（获美敦力/高瓴/启明/创新工场数亿元投资）</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.intuitive-fosun.com
-https://www.nmpa.gov.cn</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cornerstonerobotics.com
+https://www.cuhk.edu.hk</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2196,61 +2716,66 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>诺孚泰智能科技（成都）有限公司</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>四川本土对标并超越达芬奇四臂系统的五臂双操控腔镜机器人</t>
+          <t>瑞龙诺赋（上海）医疗科技有限公司（Ronovo Surgical）</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>免气腹实时力反馈五臂双操控微创腔镜手术机器人</t>
+          <t>直接对标达芬奇Xi（独创分体模块化构型更适配中国手术室）</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>独创串并混联构型机械臂设计、双操控台同步主刀协作、免气腹物理悬吊微创技术、刚性传动降本</t>
+          <t>“海山一®”（Carina）模块化分体式腔镜手术机器人系统</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>重庆大学机械与运载工程学院 / 成都天府国际生物城研发制造基地（5000㎡）</t>
+          <t>模块化独立机械臂台车架构、自由布局多专科微创手术切口、高清3D电子内窥镜</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>柏龙 教授（重庆大学博导/诺孚泰创始人兼董事长）</t>
+          <t>斯坦福大学前团队 / Intuitive资深研发专家团队 / 瑞金医院微创外科中心</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>完成中日友好医院实验动物肝胆联合切除术验证，全面推进NMPA创新医疗器械申报与人体临床试验</t>
+          <t>马长征 博士（创始人兼董事长/原Intuitive核心高管团队）</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>完成Pre-A+轮数千万元融资（创投基金重点投资）</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>四川省</t>
+          <t>获得NMPA三类医疗器械注册证（覆盖泌尿、妇科、普外、胸外四大专科全适应症）</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>完成数亿元D轮融资（知名国际产业及美元基金投资）</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>https://www.cqu.edu.cn
-https://www.bio-tianfu.com</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ronovosurgical.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2262,61 +2787,66 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>成都博恩思医学机器人有限公司</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>四川本土对标达芬奇的微创腹腔镜手术机器人</t>
+          <t>唯精医疗机器人（广东/浙江）有限公司</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统</t>
+          <t>直接对标达芬奇Xi（微创器械+耗材生态深度协同）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
+          <t>“康基唯精”腹腔镜微创手术机器人系统（SR01-200）</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
+          <t>多孔/单孔腹腔镜主从遥操作、微创多自由度吻合钳与分离剪、主手力觉传感</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
+          <t>浙江大学生物医学工程与仪器科学学院 / 广州开发区智造基地</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
+          <t>微精医疗联合创始人团队、浙江大学医工交叉科学家团队</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>四川省</t>
+          <t>SR01-200获得NMPA三类医疗器械注册证，在全国多家医院开展高难度普外泌尿微创手术</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>完成亿元级B+轮融资（微创外科龙头康基医疗战略投资）</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.biomems.com.cn
-http://www.wchscu.cn</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.weijing-robot.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2328,61 +2858,66 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>北京天智航医疗科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>对标史赛克Mako / 骨科领域“达芬奇级”多关节主从操作机器人</t>
+          <t>诺孚泰智能科技（成都）有限公司</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>“天玑”（TiRobot 1.0/2.0/3.0）骨科手术机器人系统</t>
+          <t>四川本土对标并超越达芬奇四臂系统的五臂双操控腔镜机器人</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>六自由度医用高精机械臂、光学空间定位双目双模跟踪、术中三维规划导航</t>
+          <t>免气腹实时力反馈五臂双操控微创腔镜手术机器人</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>北京航空航天大学机器人研究所 / 北京积水潭医院</t>
+          <t>独创串并混联构型机械臂设计、双操控台同步主刀协作、免气腹物理悬吊微创技术、刚性传动降本</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>田伟 院士（中国工程院院士/原积水潭医院院长）、张送根 博士、刘达 教授</t>
+          <t>重庆大学机械与运载工程学院 / 成都天府国际生物城研发制造基地（5000㎡）</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>取得多张NMPA三类医疗器械注册证，入选国家重点研发计划，全国装机量第一（超6万例）</t>
+          <t>柏龙 教授（重庆大学博导/诺孚泰创始人兼董事长）</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>科创板上市公司（688277）</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>北京市</t>
+          <t>完成中日友好医院实验动物肝胆联合切除术验证，全面推进NMPA创新医疗器械申报与人体临床试验</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>完成Pre-A+轮数千万元融资（成都市与天府生物城创投重点支持）</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>https://www.tinavi.com
-https://www.buaa.edu.cn</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cqu.edu.cn
+https://www.bio-tianfu.com</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2394,61 +2929,66 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>苏州键嘉医疗科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>对标史赛克Mako / 硬组织高精度切削手术机器人</t>
+          <t>成都博恩思医学机器人有限公司</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>“ARTHROBOT”髋膝一体全关节置换手术机器人 / “THETA”种植牙机器人</t>
+          <t>四川本土对标达芬奇的多孔微创腹腔镜及经自然腔道手术系统</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>主动力控骨质切削机械臂、双目亚毫米级红外空间跟踪、智能截骨规划算法</t>
+          <t>博恩思微创腹腔镜手术机器人系统 / 经自然腔道手术系统（TORSS）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>苏州大学医疗机器人研究所 / 俄罗斯工程院协同基地</t>
+          <t>微型主从遥控末端夹持器械、轻量化操作台、人机智能共融控制算法</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>孙立宁 院士（俄罗斯工程院外籍院士/苏大机电学院院长）、宋生林 博士</t>
+          <t>斯坦福大学前机器人团队 / 四川大学华西医院 / 电子科技大学</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>ARTHROBOT髋膝关节机器人均取得NMPA创新三类注册证，实现髋膝一体化商业装机</t>
+          <t>李耀 博士（创始人兼CEO）、曾勇 教授（华西医院副院长/肝胆胰外科主任）</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>拟IPO（高瓴/软银/百度/国药资本联合投资）</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>江苏省</t>
+          <t>完成多批次大动物试验与多中心临床前验证，处于NMPA创新医疗器械申报推进阶段</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>四川重点本土培育实体（成都高投/知名产业基金支持）</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>苏州</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.join-jia.com
-https://www.suda.edu.cn</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.biomems.com.cn
+http://www.wchscu.cn</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2460,61 +3000,66 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>元化智能科技（深圳）有限公司</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>骨科硬组织多专科“全自主切削与磨削”手术机器人</t>
+          <t>北京天智航医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>“锟铻”（KUNWU）全骨科手术机器人系统（髋/膝/单髁/脊柱全覆盖）</t>
+          <t>对标美敦力Mazor / 史赛克Mako（中国骨科手术机器人第一股）</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>全自主研发六自由度协作机械臂、双目光学导航定位仪、高动态骨组织边界保护算法</t>
+          <t>“天玑”（TiRobot 1.0/2.0/3.0）骨科手术机器人系统</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>南方科技大学机器人研究院 / 香港中文大学</t>
+          <t>六自由度医用高精机械臂、光学空间定位双目双模跟踪、术中三维规划导航</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>孟广耀 教授（创始人兼首席科学家）、孟庆虎 院士</t>
+          <t>北京航空航天大学机器人研究所 / 北京积水潭医院</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>全膝置换、全髋置换及单髁置换均获NMPA三类注册证，实现骨科多亚专科全覆盖</t>
+          <t>田伟 院士（中国工程院院士/原积水潭医院院长）、张送根 博士、刘达 教授</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>拟IPO（红杉中国/深创投联合领投）</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>广东省</t>
+          <t>取得多张NMPA三类医疗器械注册证，入选国家重点研发计划，全国装机量第一（超6万例）</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>科创板上市公司（688277）</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>https://www.genextech.cn
-https://www.sustech.edu.cn</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>https://www.tinavi.com
+https://www.buaa.edu.cn</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2526,61 +3071,66 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>华科精准（北京）医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>脑部微创外科“达芬奇级”高精度脑立体定向穿刺与消融系统</t>
+          <t>苏州键嘉医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>华科精准“SR / Q300”神经外科手术机器人 / 磁共振引导LITT激光消融系统</t>
+          <t>对标史赛克Mako / 硬组织高精度切削手术机器人</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>颅脑多模态影像三维融合、亚毫米级立体定向机械臂定位、术中激光微创热消融闭环</t>
+          <t>“ARTHROBOT”髋膝一体全关节置换手术机器人 / “THETA”种植牙机器人</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>清华大学医学院 / 首都医科大学宣武医院 / 北京天坛医院</t>
+          <t>主动力控骨质切削机械臂、双目亚毫米级红外空间跟踪、智能截骨规划算法</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>赵国光 教授（宣武医院院长）、张建民 教授（天坛医院脑科领军）</t>
+          <t>苏州大学医疗机器人研究所 / 俄罗斯工程院协同基地</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部脑科中心</t>
+          <t>孙立宁 院士（俄罗斯工程院外籍院士/苏大机电学院院长）、宋生林 博士</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>完成数亿元D轮（美敦力/红杉中国/高瓴联合投资）</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>北京市</t>
+          <t>ARTHROBOT髋膝关节机器人均取得NMPA创新三类注册证，实现髋膝一体化商业装机</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>拟IPO（高瓴/软银/百度/国药资本联合投资）</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sinovation.com
-https://www.tsinghua.edu.cn</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.join-jia.com
+https://www.suda.edu.cn</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2592,61 +3142,66 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>北京柏惠维康科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>中国最早脑立体定向手术机器人研发团队（对标法国ROSA）</t>
+          <t>元化智能科技（深圳）有限公司</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>“睿米”（Remebot）神经外科手术机器人 / “瑞医博”口腔种植手术机器人</t>
+          <t>骨科硬组织多专科“全自主切削与磨削”手术机器人（对标Mako）</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>无框架脑立体定向机械臂规划、微创多自由度导向定位、口腔亚毫米自主种植</t>
+          <t>“锟铻”（KUNWU）全骨科手术机器人系统（髋/膝/单髁/脊柱全覆盖）</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>北京航空航天大学机器人研究所 / 海军总医院</t>
+          <t>全自主研发六自由度协作机械臂、双目光学导航定位仪、高动态骨组织边界保护算法</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>王田苗 教授（北航机器人所名誉所长）、刘达 教授、刘文博 团队</t>
+          <t>南方科技大学机器人研究院 / 香港中文大学</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>获得国内首张神经外科三类医疗器械注册证，多款产品实现NMPA三类认证与全国装机</t>
+          <t>孟广耀 教授（创始人兼首席科学家）、孟庆虎 院士</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>完成D轮融资（大钲资本/中信建投/天士力资本）</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>北京市</t>
+          <t>全膝置换、全髋置换及单髁置换均获NMPA三类注册证，实现骨科多亚专科全覆盖</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>拟IPO（红杉中国/深创投联合领投）</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.remebot.com
-https://www.buaa.edu.cn</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>https://www.genextech.cn
+https://www.sustech.edu.cn</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2658,61 +3213,66 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>唯迈医疗科技（北京/天津）有限公司</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>直接对标西门子Corindus血管介入手术机器人</t>
+          <t>深圳市鑫君特智能医疗器械有限公司</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>“ETcath”血管介入手术机器人系统 / 极光平板DSA大型微创造影平台</t>
+          <t>中国首款具备“导航+主动置针操作”全智能骨科手术机器人（对标Mazor）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>介入导管导丝多自由度智能推进操控、微小力觉触觉双向反馈、全流程低剂量防辐射操控</t>
+          <t>“ORTHBOT®”智能脊柱骨科手术机器人系统</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>北京理工大学医工融合研究院 / 日本工程院院士工作站</t>
+          <t>多模态影像融合、自动钉道规划、主动进针伺服控制、压力监测防破壁保护</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>郭书祥 院士（日本工程院院士/北理工教授）、杨海宏 博士</t>
+          <t>中国科学院深圳先进技术研究院 / 深圳市脊柱微创工程中心</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类注册证并完成多中心PCI人体手术</t>
+          <t>姜轶 董事长兼研发带头人、国内顶级脊柱骨科专家团队</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>完成数亿元D轮融资（国药资本/华兴资本/浩悦资本）</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>北京市</t>
+          <t>获得NMPA三类医疗器械注册证，并于2023年斩获中国首张欧盟MDR CE认证脊柱机器人证书</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元B轮与战略融资（知名医疗创投基金投资）</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.wemedmed.com
-https://www.bit.edu.cn</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.futurtec.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2724,61 +3284,66 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>上海奥朋医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>对标西门子Corindus / 泛血管主从遥操作介入手术机器人</t>
+          <t>北京长木谷医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>“ALLVAS”泛血管介入手术机器人系统（冠脉/外周/脑血管全覆盖）</t>
+          <t>骨科AI智能规划+高精度关节置换手术机器人（对标Mako）</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>多轴主从力反馈介入执行端、多规格导丝导管通用夹持机构、亚毫米级送丝步进控制</t>
+          <t>“ROPA”全膝/全髋关节置换手术机器人 / AIJOINT骨科三维规划系统</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>复旦大学附属中山医院心内科 / 上海交通大学</t>
+          <t>深度学习骨科CT影像三维建模、亚毫米级动力截骨机械臂、术中假体姿态自适应校准</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>葛均波 院士（中国科学院院士/中山医院心内科主任）、刘冰 博士</t>
+          <t>清华大学医学院 / 积水潭医院骨科工程转化平台</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>进入NMPA创新医疗器械特别审批程序，成功完成多例人体冠脉微创PCI手术</t>
+          <t>张戟 董事长、国内顶级关节外科专家协同团队</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>完成超亿元B轮融资（高瓴创投/保诺资本投资）</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>上海市</t>
+          <t>ROPA全膝及全髋手术机器人获NMPA创新三类医疗器械注册证，数百家三甲医院常规使用</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>完成数亿元B+轮及C轮融资（中金资本/联想创投/软银中国投资）</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.allwamed.com
-http://www.zs-hospital.sh.cn</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>https://www.deepmotion.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2790,61 +3355,66 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>真健康（北京）医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>经皮穿刺与肿瘤微创介入“达芬奇级”多自由度机械臂消融系统</t>
+          <t>苏州铸正机器人有限公司</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>“穿刺手术导航定位系统” / 经皮穿刺活检消融手术机器人</t>
+          <t>脊柱微创高精度“全流程自动识切”手术机器人</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CT/超声术中多模态影像三维融合、呼吸运动补偿追踪、高柔顺性穿刺机械臂控制</t>
+          <t>“佐航300/500”脊柱外科手术导航定位与自主切削机器人系统</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>清华大学 / 中国医学科学院肿瘤医院</t>
+          <t>高精度光学立体定位、亚毫米级（≤0.8mm）骨科微创机械臂、术中骨解剖自动识别算法</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>张世阳 博士（联合创始人兼CTO）、国内肿瘤微创介入专家团队</t>
+          <t>北京航空航天大学医疗机器人实验室 / 苏州高新区转化基地</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>获NMPA创新医疗器械三类注册证，在全国头部三甲医院开展数千例肺结节精准活检手术</t>
+          <t>北航医疗机器人科研骨干团队</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>完成数亿元B+轮与Pre-IPO融资</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>北京市</t>
+          <t>佐航300及佐航500均已获得NMPA三类医疗器械注册证（国械注准20223010268）</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>完成数千万元A轮融资（中科院及高校创投基金支持）</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.truemed-tech.com
-https://www.tsinghua.edu.cn</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.zoezen.cn
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2856,61 +3426,66 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>四川华西精创医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>四川本地顶尖医工转化标杆（对标美敦力StealthStation）</t>
+          <t>北京和华瑞博医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>“华西精准”骨科手术导航系统 / 经皮穿刺与胸外科微创手术定位机器人</t>
+          <t>对标史赛克Mako / 关节精准力控截骨手术机器人</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>光学三维空间立体定位、脊柱/关节穿刺轨迹智能规划、医用机械臂微创导向</t>
+          <t>“和华”（Hopesync）全膝关节置换手术机器人系统</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>四川大学华西医院 / 国家精准医学产业创新中心</t>
+          <t>主动式连续截骨机械臂、多模态导航注册算法、软组织平衡精准力学评估</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>裴福兴 教授（华西骨科领军）、李为民 教授（华西呼吸内科领军）</t>
+          <t>清华大学机械工程系 / 中国医学科学院北京协和医院</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>依托华西医院多中心临床资源推进三类医疗器械注册与规模化临床试验</t>
+          <t>清华大学医工交叉团队 / 协和骨科专家团队</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>华西医院科技成果转化实体（省属产业基金战略孵化）</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>四川省</t>
+          <t>获得NMPA三类医疗器械注册证，在全国数十家三甲医院开展关节置换临床应用</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>完成数亿元B轮融资（启明创投/红杉中国等投资）</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>http://www.wchscu.cn
-https://www.scu.edu.cn</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hopesync.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2922,61 +3497,705 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>苏州迪凯尔医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>硬组织高精度口腔专科“达芬奇级”自主种植手术机器人</t>
+          <t>北京罗森博特科技有限公司</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>“易植美”（DCarer）口腔种植手术机器人 / 光学三维手术导航系统</t>
+          <t>全球首创创伤骨科深部骨折“智能闭合复位”手术机器人</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>光学高频双目空间追踪、全自主种植切削轨迹伺服、口腔微空间力觉安全边界保护</t>
+          <t>“罗森博特”骨折复位创伤骨科手术机器人系统</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>苏州大学机电工程学院 / 空军军医大学第三附属医院（口腔医学院）</t>
+          <t>多机械臂力控协同复位、术中三维应力感知、骨折远近端骨折块三维位姿自动对齐</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>陈新湖 博士（创始人兼CEO）、赵铱民 院士团队产学研协同</t>
+          <t>北京航空航天大学机器人研究所 / 北京积水潭医院创伤骨科</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>获NMPA三类医疗器械注册证，在全国数百家口腔专科医院规模化临床装机</t>
+          <t>王田苗 教授、吴新宝 教授（积水潭医院副院长/创伤骨科主委）</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>拟IPO（完成数亿元C轮融资）</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
+          <t>获得NMPA创新医疗器械特别审查绿色通道，进入多中心临床试验与注册审评</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>完成超亿元Pre-A及A轮融资（知名产业基金领投）</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rosenbot.cn
+https://www.buaa.edu.cn</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>四川华西精创医疗科技有限公司 / 华西医疗机器人研究院</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>四川本地登顶《Science Robotics》顶刊的柔性脊柱与骨科导航微创手术机器人</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>“MicroSpine”柔性脊柱微创手术机器人 / 华西精准骨科手术导航系统</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>超冗余柔性连续体机械臂、微创经皮穿刺自动轨迹规划、多模态光学三维空间立体定位</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>四川大学华西医院 / 华西医疗机器人研究院 / 国家精准医学产业创新中心</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>裴福兴 教授（华西骨科领军/中华骨科分会前主委）、李为民 教授</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>MicroSpine成果发表于《Science Robotics》，骨科导航与穿刺系统推进三类器械注册申报</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>成都高新区岷山行动计划资助（华西医院科技成果转化实体）</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>http://www.wchscu.cn
+https://www.scu.edu.cn</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>华科精准（北京）医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>脑部微创外科“达芬奇级”高精度脑立体定向穿刺与激光消融系统</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>华科精准“SR / Q300”神经外科手术机器人 / 磁共振引导LITT激光消融系统</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>颅脑多模态影像三维融合、亚毫米级立体定向机械臂定位、术中激光微创热消融闭环</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>清华大学医学院 / 首都医科大学宣武医院 / 北京天坛医院</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>赵国光 教授（宣武医院院长）、张建民 教授（天坛医院脑科领军）</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部三甲脑科中心</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元D轮（美敦力/红杉中国/高瓴联合投资）</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sinovation.com
+https://www.tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>北京柏惠维康科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>中国最早脑立体定向手术机器人研发团队（对标法国ROSA）</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>“睿米”（Remebot）神经外科手术机器人 / “瑞医博”口腔种植手术机器人</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>无框架脑立体定向机械臂规划、微创多自由度导向定位、口腔亚毫米自主种植</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>北京航空航天大学机器人研究所 / 海军总医院</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>王田苗 教授（北航机器人所名誉所长）、刘达 教授、刘文博 团队</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>获得国内首张神经外科三类医疗器械注册证，多款产品实现NMPA三类认证与全国装机</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>完成D轮融资（大钲资本/中信建投/天士力资本）</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>https://www.remebot.com
+https://www.buaa.edu.cn</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>北京华志微创医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>中国首个自主知识产权脑立体定向微创手术机器人（对标ROSA）</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>“CAS-R-2”无框架脑立体定向手术机器人系统</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>高精度光学立体空间定位、微创颅脑穿刺机械臂导向、多模态手术路径规划</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>中国科学院自动化研究所 / 海军总医院神经外科转化团队</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>田增民 教授（原海军总医院神经外科主任/全军创伤脑科中心主任）</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>获NMPA三类医疗器械注册证，累计完成脑深部微创手术上万例</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>完成数千万元B轮融资（国科嘉和/深创投投资）</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cas-r.com
+http://www.ia.cas.cn</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>杭州佳量医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>脑部微创癫痫与脑胶质瘤“磁共振实时测温+光纤激光消融”手术系统（对标美敦力Visualase）</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>磁共振引导颅脑微创“LITT”激光消融手术机器人系统</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>术中实时磁共振温度监控场、柔性水冷激光光纤传动、亚毫米级穿刺导向定位</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>浙江大学脑机交互与神经工程中心 / 浙江大学医学院附属第二医院</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>王跃明 教授（浙大博导）、张建民 教授（浙大二院神经外科主任）</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类医疗器械注册证并开展多例脑瘤消融</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>完成数亿元B轮融资（知名医疗投资基金领投）</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>浙江省</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jialiangmed.com
+https://www.zju.edu.cn</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>唯迈医疗科技（北京/天津）有限公司</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>直接对标西门子Corindus血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>“ETcath”血管介入手术机器人系统 / 极光平板DSA大型微创造影平台</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>介入导管导丝多自由度智能推进操控、微小力觉触觉双向反馈、全流程低剂量防辐射操控</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>北京理工大学医工融合研究院 / 日本工程院院士工作站</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>郭书祥 院士（日本工程院院士/北理工教授）、杨海宏 博士</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类注册证并完成多中心PCI人体手术</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元D轮融资（国药资本/华兴资本/浩悦资本）</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wemedmed.com
+https://www.bit.edu.cn</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>上海奥朋医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>对标西门子Corindus / 泛血管主从遥操作介入手术机器人</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>“ALLVAS”泛血管介入手术机器人系统（冠脉/外周/脑血管全覆盖）</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>多轴主从力反馈介入执行端、多规格导丝导管通用夹持机构、亚毫米级送丝步进控制</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>复旦大学附属中山医院心内科 / 上海交通大学</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>葛均波 院士（中国科学院院士/中山医院心内科主任）、刘冰 博士</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>进入NMPA创新医疗器械特别审批程序，成功完成多例人体冠脉微创PCI手术</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>完成超亿元B轮融资（高瓴创投/保诺资本投资）</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>https://www.allwamed.com
+http://www.zs-hospital.sh.cn</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>苏州梅奥心磁医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>直接对标强生/Stereotaxis磁控心脏电生理介入手术机器人</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>“TITIAN”磁控心律失常电生理介入消融手术机器人系统</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>外部旋转可调磁场导航、磁性微创导管柔性姿态操控、心内三维电解剖标测</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>苏州大学心血管病研究所 / 上海交通大学医学院附属瑞金医院</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>陈梅 博士（创始人兼CEO）、国内顶级心律失常电生理专家</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>进入创新医疗器械申报，成功完成人体磁控心房颤动射频消融手术验证</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>完成数千万元A+轮融资（知名医疗创投基金投资）</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>江苏省</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>苏州</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.dcarer.com
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mayomagnetic.com
 https://www.suda.edu.cn</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>真健康（北京）医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>经皮穿刺手术机器人</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>经皮穿刺与肿瘤微创介入“达芬奇级”多自由度机械臂消融系统</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>“穿刺手术导航定位系统” / 经皮穿刺活检消融手术机器人</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>CT/超声术中多模态影像三维融合、呼吸运动补偿追踪、高柔顺性穿刺机械臂控制</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>清华大学 / 中国医学科学院肿瘤医院</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>张世阳 博士（联合创始人兼CTO）、国内肿瘤微创介入专家团队</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>获NMPA创新医疗器械三类注册证，在全国头部三甲医院开展数千例肺结节精准活检手术</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>完成数亿元B+轮与Pre-IPO融资</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>https://www.truemed-tech.com
+https://www.tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2993,22 +4212,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3024,55 +4244,60 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -3087,58 +4312,63 @@
           <t>北京术锐技术股份有限公司</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>直接对标达芬奇SP（Da Vinci Single Port）单孔手术系统</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>“术锐”（Surgerii SR-CNS-100）单孔腔镜手术机器人</t>
-        </is>
-      </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>“术锐”（Surgerii SR-CNS-100/SR-ENS-600）单孔腔镜手术机器人</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>高刚性蛇形连续体结构机构、多自由度微创蛇形器械、单孔多通道主从操控</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>上海交通大学机械与动力工程学院机器人研究所</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>徐凯 教授（交大博导/术锐创始人兼首席科学家）</t>
-        </is>
-      </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
+          <t>徐凯 教授（交大博导/国家杰青/术锐创始人兼首席科学家）</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
           <t>国内首个获批NMPA三类注册证的蛇形臂单孔腔镜手术系统（进入国家创新医疗器械特别审查绿色通道）</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>拟IPO（完成C轮数亿元融资，美敦力/国投招商投资）</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>https://www.surgerii.com
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3153,58 +4383,63 @@
           <t>北京天智航医疗科技股份有限公司</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>对标史赛克Mako / 骨科领域“达芬奇级”多关节主从操作机器人</t>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
+          <t>对标美敦力Mazor / 史赛克Mako（中国骨科手术机器人第一股）</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
           <t>“天玑”（TiRobot 1.0/2.0/3.0）骨科手术机器人系统</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>六自由度医用高精机械臂、光学空间定位双目双模跟踪、术中三维规划导航</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>北京航空航天大学机器人研究所 / 北京积水潭医院</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>田伟 院士（中国工程院院士/原积水潭医院院长）、张送根 博士、刘达 教授</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>取得多张NMPA三类医疗器械注册证，入选国家重点研发计划，全国装机量第一（超6万例）</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>科创板上市公司（688277）</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>https://www.tinavi.com
 https://www.buaa.edu.cn</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3216,61 +4451,66 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>华科精准（北京）医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>脑部微创外科“达芬奇级”高精度脑立体定向穿刺与消融系统</t>
+          <t>北京长木谷医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>华科精准“SR / Q300”神经外科手术机器人 / 磁共振引导LITT激光消融系统</t>
+          <t>骨科AI智能规划+高精度关节置换手术机器人（对标Mako）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>颅脑多模态影像三维融合、亚毫米级立体定向机械臂定位、术中激光微创热消融闭环</t>
+          <t>“ROPA”全膝/全髋关节置换手术机器人 / AIJOINT骨科三维规划系统</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>清华大学医学院 / 首都医科大学宣武医院 / 北京天坛医院</t>
+          <t>深度学习骨科CT影像三维建模、亚毫米级动力截骨机械臂、术中假体姿态自适应校准</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>赵国光 教授（宣武医院院长）、张建民 教授（天坛医院脑科领军）</t>
+          <t>清华大学医学院 / 积水潭医院骨科工程转化平台</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部脑科中心</t>
+          <t>张戟 董事长、国内顶级关节外科专家协同团队</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>完成数亿元D轮（美敦力/红杉中国/高瓴联合投资）</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
+          <t>ROPA全膝及全髋手术机器人获NMPA创新三类医疗器械注册证，数百家三甲医院常规使用</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元B+轮及C轮融资（中金资本/联想创投/软银中国投资）</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sinovation.com
-https://www.tsinghua.edu.cn</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.deepmotion.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3282,61 +4522,66 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>北京柏惠维康科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>中国最早脑立体定向手术机器人研发团队（对标法国ROSA）</t>
+          <t>北京和华瑞博医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>“睿米”（Remebot）神经外科手术机器人 / “瑞医博”口腔种植手术机器人</t>
+          <t>对标史赛克Mako / 关节精准力控截骨手术机器人</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>无框架脑立体定向机械臂规划、微创多自由度导向定位、口腔亚毫米自主种植</t>
+          <t>“和华”（Hopesync）全膝关节置换手术机器人系统</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>北京航空航天大学机器人研究所 / 海军总医院</t>
+          <t>主动式连续截骨机械臂、多模态导航注册算法、软组织平衡精准力学评估</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>王田苗 教授（北航机器人所名誉所长）、刘达 教授、刘文博 团队</t>
+          <t>清华大学机械工程系 / 中国医学科学院北京协和医院</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>获得国内首张神经外科三类医疗器械注册证，多款产品实现NMPA三类认证与全国装机</t>
+          <t>清华大学医工交叉团队 / 协和骨科专家团队</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>完成D轮融资（大钲资本/中信建投/天士力资本）</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
+          <t>获得NMPA三类医疗器械注册证，在全国数十家三甲医院开展关节置换临床应用</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>完成数亿元B轮融资（启明创投/红杉中国等投资）</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>https://www.remebot.com
-https://www.buaa.edu.cn</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hopesync.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3348,61 +4593,66 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>唯迈医疗科技（北京/天津）有限公司</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>直接对标西门子Corindus血管介入手术机器人</t>
+          <t>北京罗森博特科技有限公司</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>“ETcath”血管介入手术机器人系统 / 极光平板DSA大型微创造影平台</t>
+          <t>全球首创创伤骨科深部骨折“智能闭合复位”手术机器人</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>介入导管导丝多自由度智能推进操控、微小力觉触觉双向反馈、全流程低剂量防辐射操控</t>
+          <t>“罗森博特”骨折复位创伤骨科手术机器人系统</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>北京理工大学医工融合研究院 / 日本工程院院士工作站</t>
+          <t>多机械臂力控协同复位、术中三维应力感知、骨折远近端骨折块三维位姿自动对齐</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>郭书祥 院士（日本工程院院士/北理工教授）、杨海宏 博士</t>
+          <t>北京航空航天大学机器人研究所 / 北京积水潭医院创伤骨科</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类注册证并完成多中心PCI人体手术</t>
+          <t>王田苗 教授、吴新宝 教授（积水潭医院副院长/创伤骨科主委）</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>完成数亿元D轮融资（国药资本/华兴资本/浩悦资本）</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
+          <t>获得NMPA创新医疗器械特别审查绿色通道，进入多中心临床试验与注册审评</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>完成超亿元Pre-A及A轮融资（知名产业基金领投）</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.wemedmed.com
-https://www.bit.edu.cn</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rosenbot.cn
+https://www.buaa.edu.cn</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3414,61 +4664,350 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
+          <t>华科精准（北京）医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>脑部微创外科“达芬奇级”高精度脑立体定向穿刺与激光消融系统</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>华科精准“SR / Q300”神经外科手术机器人 / 磁共振引导LITT激光消融系统</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>颅脑多模态影像三维融合、亚毫米级立体定向机械臂定位、术中激光微创热消融闭环</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>清华大学医学院 / 首都医科大学宣武医院 / 北京天坛医院</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>赵国光 教授（宣武医院院长）、张建民 教授（天坛医院脑科领军）</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>拥有多张NMPA三类医疗器械注册证与FDA认证，进入全国200余家头部三甲脑科中心</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>完成数亿元D轮（美敦力/红杉中国/高瓴联合投资）</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sinovation.com
+https://www.tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>北京柏惠维康科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>中国最早脑立体定向手术机器人研发团队（对标法国ROSA）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>“睿米”（Remebot）神经外科手术机器人 / “瑞医博”口腔种植手术机器人</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>无框架脑立体定向机械臂规划、微创多自由度导向定位、口腔亚毫米自主种植</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>北京航空航天大学机器人研究所 / 海军总医院</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>王田苗 教授（北航机器人所名誉所长）、刘达 教授、刘文博 团队</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>获得国内首张神经外科三类医疗器械注册证，多款产品实现NMPA三类认证与全国装机</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>完成D轮融资（大钲资本/中信建投/天士力资本）</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.remebot.com
+https://www.buaa.edu.cn</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>北京华志微创医疗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>中国首个自主知识产权脑立体定向微创手术机器人（对标ROSA）</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>“CAS-R-2”无框架脑立体定向手术机器人系统</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>高精度光学立体空间定位、微创颅脑穿刺机械臂导向、多模态手术路径规划</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>中国科学院自动化研究所 / 海军总医院神经外科转化团队</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>田增民 教授（原海军总医院神经外科主任/全军创伤脑科中心主任）</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>获NMPA三类医疗器械注册证，累计完成脑深部微创手术上万例</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>完成数千万元B轮融资（国科嘉和/深创投投资）</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cas-r.com
+http://www.ia.cas.cn</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>唯迈医疗科技（北京/天津）有限公司</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>直接对标西门子Corindus血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>“ETcath”血管介入手术机器人系统 / 极光平板DSA大型微创造影平台</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>介入导管导丝多自由度智能推进操控、微小力觉触觉双向反馈、全流程低剂量防辐射操控</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>北京理工大学医工融合研究院 / 日本工程院院士工作站</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>郭书祥 院士（日本工程院院士/北理工教授）、杨海宏 博士</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类注册证并完成多中心PCI人体手术</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元D轮融资（国药资本/华兴资本/浩悦资本）</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wemedmed.com
+https://www.bit.edu.cn</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
           <t>真健康（北京）医疗科技有限公司</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>经皮穿刺手术机器人</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>经皮穿刺与肿瘤微创介入“达芬奇级”多自由度机械臂消融系统</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>“穿刺手术导航定位系统” / 经皮穿刺活检消融手术机器人</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>CT/超声术中多模态影像三维融合、呼吸运动补偿追踪、高柔顺性穿刺机械臂控制</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>清华大学 / 中国医学科学院肿瘤医院</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>张世阳 博士（联合创始人兼CTO）、国内肿瘤微创介入专家团队</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>获NMPA创新医疗器械三类注册证，在全国头部三甲医院开展数千例肺结节精准活检手术</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>完成数亿元B+轮与Pre-IPO融资</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>https://www.truemed-tech.com
 https://www.tsinghua.edu.cn</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="N11" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3485,22 +5024,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3516,55 +5056,60 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -3579,58 +5124,63 @@
           <t>哈尔滨思哲睿智能医疗设备股份有限公司</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>直接对标达芬奇（Da Vinci Xi）多孔腹腔镜手术系统</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>“康多机器人”（KangDuo Robot KD-SR-01/02）多孔及单孔腹腔镜手术系统</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>主从构型空间解耦控制、开放式医生控制台、自适应从动多臂协作机构</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>哈尔滨工业大学机器人技术与系统国家重点实验室</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>杜志江 教授（哈工大机器人所副所长/思哲睿首席科学家）、孙立宁 院士</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>获国家创新医疗器械特别审查，取得多张NMPA三类医疗器械注册证，累计完成数千例手术</t>
-        </is>
-      </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
+          <t>获国家创新医疗器械特别审查，取得多张NMPA三类医疗器械注册证与首张CB证书，完成数千例手术</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
           <t>科创板申报（深创投/中金资本投资）</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>黑龙江省</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>哈尔滨</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>https://www.hit.edu.cn
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3647,22 +5197,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3678,55 +5229,60 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -3738,61 +5294,66 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上海微创医疗机器人（集团）股份有限公司</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇（Da Vinci Xi/Si）多孔腔镜手术系统</t>
+          <t>直观复星医疗器械技术（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>“图迈”（Toumai）多孔腔镜手术机器人 / “鸿鹄”骨科手术机器人</t>
+          <t>全球手术机器人绝对黄金标杆（达芬奇原厂中国本土化制造基地）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>多臂微创腹腔镜主从遥操作系统、高精度主手控制台、裸眼3D立体内窥镜</t>
+          <t>达芬奇“Da Vinci Xi / SP”国产化手术系统制造与创新研发</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>上海交通大学医疗机器人研究院 / 中科院微系统所</t>
+          <t>四臂主从遥操作系统、EndoWrist多自由度仿真手腕、高清沉浸式3D双目内窥镜</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>何超 博士（上海微创机器人总裁）、戴尅戎 院士团队</t>
+          <t>直观复星张江创新研发制造基地 / 复旦大学附属中山医院医工转化中心</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>图迈多孔获NMPA三类注册证（中国首个覆盖泌尿、普外、胸外、妇科全科室腔镜机器人）；鸿鹄获NMPA+FDA+CE认证</t>
+          <t>Intuitive全球科学家团队 + 葛均波/樊嘉 院士团队</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>港股上市公司（02252.HK）</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
+          <t>达芬奇Xi系统获NMPA国产化三类医疗器械注册证，在上海张江正式实现国产化量产下线</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>达芬奇原厂Intuitive Surgical与复星医药合资</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>上海市</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.medrobotics.com
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.intuitive-fosun.com
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3804,61 +5365,66 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>直观复星医疗器械技术（上海）有限公司</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>全球手术机器人绝对黄金标杆（达芬奇原厂中国本土化制造）</t>
+          <t>上海微创医疗机器人（集团）股份有限公司</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>达芬奇“Da Vinci Xi / SP”国产化手术系统制造与创新研发</t>
+          <t>直接对标达芬奇（Da Vinci Xi/Si）多孔腔镜微创手术系统</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>四臂主从遥操作系统、EndoWrist多自由度仿真手腕、高清沉浸式3D双目内窥镜</t>
+          <t>“图迈”（Toumai）多孔腔镜手术机器人 / “鸿鹄”骨科手术机器人</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>直观复星张江创新研发基地 / 复旦大学附属中山医院医工转化中心</t>
+          <t>多臂微创腹腔镜主从遥操作系统、高精度主手控制台、裸眼3D立体内窥镜</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>全球Intuitive工程研发科学家团队 + 葛均波/樊嘉 院士团队</t>
+          <t>上海交通大学医疗机器人研究院 / 中科院微系统所</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>达芬奇Xi系统获NMPA国产化三类医疗器械注册证，在上海张江正式实现国产化量产下线</t>
+          <t>何超 博士（上海微创机器人总裁）、戴尅戎 院士团队</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>达芬奇原厂Intuitive Surgical与复星医药合资</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
+          <t>图迈多孔获NMPA三类注册证（中国首个覆盖泌尿、普外、胸外、妇科全科室腔镜机器人）；鸿鹄获NMPA+FDA+CE认证</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>港股上市公司（02252.HK）</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>上海市</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>https://www.intuitive-fosun.com
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.medrobotics.com
 https://www.nmpa.gov.cn</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3870,61 +5436,137 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>瑞龙诺赋（上海）医疗科技有限公司（Ronovo Surgical）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>直接对标达芬奇Xi（独创分体模块化构型更适配中国手术室）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>“海山一®”（Carina）模块化分体式腔镜手术机器人系统</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>模块化独立机械臂台车架构、自由布局多专科微创手术切口、高清3D电子内窥镜</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>斯坦福大学前团队 / Intuitive资深研发专家团队 / 瑞金医院微创外科中心</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>马长征 博士（创始人兼董事长/原Intuitive核心高管团队）</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>获得NMPA三类医疗器械注册证（覆盖泌尿、妇科、普外、胸外四大专科全适应症）</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元D轮融资（知名国际产业及美元基金投资）</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ronovosurgical.com
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
           <t>上海奥朋医疗科技有限公司</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>对标西门子Corindus / 泛血管主从遥操作介入手术机器人</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>“ALLVAS”泛血管介入手术机器人系统（冠脉/外周/脑血管全覆盖）</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>多轴主从力反馈介入执行端、多规格导丝导管通用夹持机构、亚毫米级送丝步进控制</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>复旦大学附属中山医院心内科 / 上海交通大学</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>葛均波 院士（中国科学院院士/中山医院心内科主任）、刘冰 博士</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>进入NMPA创新医疗器械特别审批程序，成功完成多例人体冠脉微创PCI手术</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>完成超亿元B轮融资（高瓴创投/保诺资本投资）</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>上海市</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>https://www.allwamed.com
 http://www.zs-hospital.sh.cn</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -3941,22 +5583,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3972,55 +5615,60 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -4035,58 +5683,63 @@
           <t>苏州键嘉医疗科技股份有限公司</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>对标史赛克Mako / 硬组织高精度切削手术机器人</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>“ARTHROBOT”髋膝一体全关节置换手术机器人 / “THETA”种植牙机器人</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>主动力控骨质切削机械臂、双目亚毫米级红外空间跟踪、智能截骨规划算法</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>苏州大学医疗机器人研究所 / 俄罗斯工程院协同基地</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>孙立宁 院士（俄罗斯工程院外籍院士/苏大机电学院院长）、宋生林 博士</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>ARTHROBOT髋膝关节机器人均取得NMPA创新三类注册证，实现髋膝一体化商业装机</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>拟IPO（高瓴/软银/百度/国药资本联合投资）</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>江苏省</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>苏州</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>https://www.join-jia.com
 https://www.suda.edu.cn</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -4098,61 +5751,137 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>苏州迪凯尔医疗科技有限公司</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>硬组织高精度口腔专科“达芬奇级”自主种植手术机器人</t>
+          <t>苏州铸正机器人有限公司</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>骨科手术机器人</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>“易植美”（DCarer）口腔种植手术机器人 / 光学三维手术导航系统</t>
+          <t>脊柱微创高精度“全流程自动识切”手术机器人</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>光学高频双目空间追踪、全自主种植切削轨迹伺服、口腔微空间力觉安全边界保护</t>
+          <t>“佐航300/500”脊柱外科手术导航定位与自主切削机器人系统</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>苏州大学机电工程学院 / 空军军医大学第三附属医院（口腔医学院）</t>
+          <t>高精度光学立体定位、亚毫米级（≤0.8mm）骨科微创机械臂、术中骨解剖自动识别算法</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>陈新湖 博士（创始人兼CEO）、赵铱民 院士团队产学研协同</t>
+          <t>北京航空航天大学医疗机器人实验室 / 苏州高新区转化基地</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>获NMPA三类医疗器械注册证，在全国数百家口腔专科医院规模化临床装机</t>
+          <t>北航医疗机器人科研骨干团队</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>拟IPO（完成数亿元C轮融资）</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
+          <t>佐航300及佐航500均已获得NMPA三类医疗器械注册证（国械注准20223010268）</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>完成数千万元A轮融资（中科院及高校创投基金支持）</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>江苏省</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>苏州</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>https://www.dcarer.com
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.zoezen.cn
+https://www.nmpa.gov.cn</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>苏州梅奥心磁医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>血管介入手术机器人</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>直接对标强生/Stereotaxis磁控心脏电生理介入手术机器人</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>“TITIAN”磁控心律失常电生理介入消融手术机器人系统</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>外部旋转可调磁场导航、磁性微创导管柔性姿态操控、心内三维电解剖标测</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>苏州大学心血管病研究所 / 上海交通大学医学院附属瑞金医院</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>陈梅 博士（创始人兼CEO）、国内顶级心律失常电生理专家</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>进入创新医疗器械申报，成功完成人体磁控心房颤动射频消融手术验证</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>完成数千万元A+轮融资（知名医疗创投基金投资）</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>江苏省</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mayomagnetic.com
 https://www.suda.edu.cn</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -4169,22 +5898,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4200,55 +5930,60 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -4260,61 +5995,66 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>山东威高手术机器人有限公司</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>中国首个自主研发主从腔镜手术系统（对标达芬奇Xi）</t>
+          <t>杭州佳量医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>神经外科手术机器人</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>“妙手S”（MicroHand S）多孔微创腹腔镜手术机器人系统</t>
+          <t>脑部微创癫痫与脑胶质瘤“磁共振实时测温+光纤激光消融”手术系统（对标美敦力Visualase）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>多自由度微创手术末端器械、主从异构映射算法、5G超远程手术通信操控</t>
+          <t>磁共振引导颅脑微创“LITT”激光消融手术机器人系统</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>天津大学机械工程学院 / 重庆大学</t>
+          <t>术中实时磁共振温度监控场、柔性水冷激光光纤传动、亚毫米级穿刺导向定位</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>王树新 院士（中国工程院院士/原天大副校长/重大校长）</t>
+          <t>浙江大学脑机交互与神经工程中心 / 浙江大学医学院附属第二医院</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>国内首批获批NMPA三类注册证的国产腹腔镜手术机器人，完成国际首例5G远程人体手术</t>
+          <t>王跃明 教授（浙大博导）、张建民 教授（浙大二院神经外科主任）</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>威高骨干产业实体（威高集团核心高端板块）</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>山东省</t>
+          <t>获国家创新医疗器械特别审查绿色通道，取得NMPA三类医疗器械注册证并开展多例脑瘤消融</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>完成数亿元B轮融资（知名医疗投资基金领投）</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>威海</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.wego.com.cn
-https://www.tju.edu.cn</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
+          <t>浙江省</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jialiangmed.com
+https://www.zju.edu.cn</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -4331,22 +6071,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4362,55 +6103,60 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>细分手术赛道</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
           <t>对标国际标杆（达芬奇等）</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>旗舰手术机器人产品</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>核心技术路线与优势</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>依托高校院所研发平台</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>科学家/学术带头人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>临床注册/NMPA阶段</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>资本与融资背景</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>所属省份</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>总部城市</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>公开来源</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>核验日期</t>
         </is>
@@ -4422,193 +6168,66 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>深圳市精锋医疗科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇Xi（多孔）与达芬奇SP（单孔）双产品线</t>
+          <t>山东威高手术机器人有限公司</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>腔镜微创手术机器人</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>精锋“MP1000”多孔腔镜手术机器人 / “SP1000”单孔腔镜手术机器人</t>
+          <t>中国首个自主研发主从腔镜手术系统（对标达芬奇Xi）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>主从双向遥操作系统、高分辨率3D电子内窥镜、全自主自研伺服多自由度手术臂</t>
+          <t>“妙手S”（MicroHand S）多孔微创腹腔镜手术机器人系统</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>香港中文大学天石机器人研究所 / 南方科技大学</t>
+          <t>多自由度微创手术末端器械、主从异构映射算法、5G超远程手术通信操控</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>王建辰 博士（创始人兼董事长）、孟庆虎 院士、刘云辉 教授</t>
+          <t>天津大学机械工程学院 / 重庆大学</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>MP1000多孔及SP1000单孔均获NMPA三类医疗器械注册证，实现多孔/单孔双证闭环</t>
+          <t>王树新 院士（中国工程院院士/原天大副校长/重大校长）</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>拟IPO（淡马锡/红杉中国/腾讯/博裕联合投资）</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>广东省</t>
+          <t>国内首批获批NMPA三类注册证的国产腹腔镜手术机器人，完成国际首例5G远程人体手术</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>威高骨干产业实体（威高集团核心高端板块）</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.edge-medical.com
-https://www.nmpa.gov.cn</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>康诺思腾（Cornerstone Robotics）</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>直接对标达芬奇高端多专科微创手术系统</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>“Sentire”多孔及单孔微创腔镜手术机器人系统</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>自主柔性连续体动力传动、模块化轻量化机械臂、全自主底层软硬件平台</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>香港中文大学机械与自动化工程学系 / 深圳研发基地</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>欧国威 教授（前达芬奇原厂Intuitive核心研发总监/港中文教授）</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>获得NMPA三类医疗器械注册证与CE认证，全球多中心临床手术开展</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>拟IPO（获美敦力/高瓴/启明/创新工场数亿元投资）</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>广东省</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>https://www.cornerstonerobotics.com
-https://www.cuhk.edu.hk</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>元化智能科技（深圳）有限公司</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>骨科硬组织多专科“全自主切削与磨削”手术机器人</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>“锟铻”（KUNWU）全骨科手术机器人系统（髋/膝/单髁/脊柱全覆盖）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>全自主研发六自由度协作机械臂、双目光学导航定位仪、高动态骨组织边界保护算法</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>南方科技大学机器人研究院 / 香港中文大学</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>孟广耀 教授（创始人兼首席科学家）、孟庆虎 院士</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>全膝置换、全髋置换及单髁置换均获NMPA三类注册证，实现骨科多亚专科全覆盖</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>拟IPO（红杉中国/深创投联合领投）</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>广东省</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.genextech.cn
-https://www.sustech.edu.cn</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>威海</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wego.com.cn
+https://www.tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
